--- a/frame_model.xlsx
+++ b/frame_model.xlsx
@@ -10,15 +10,19 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Members" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Supports" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NodalLoads" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="PointLoads" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="UDLs" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Reactions" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Displacements" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Diagrams" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Sections" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Supports" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NodalLoads" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PointLoads" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="UDLs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Reactions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Displacements" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Summary" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Diagrams" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="SectionNames">Sections!$A$2:$A$101</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -440,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -483,84 +487,98 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Members      -- id, node_i, node_j, E (modulus), A (area), I (moment of inertia), hinge_i/hinge_j (TRUE releases that end's moment connection, e.g. for truss bars)</t>
+          <t xml:space="preserve">  Members      -- id, node_i, node_j, section, E, A, I, hinge_i/hinge_j. EITHER pick a section from the dropdown and leave E/A/I blank (properties come from the Sections sheet), OR leave section blank and type E (modulus), A (area), I (moment of inertia) yourself. hinge_i/hinge_j TRUE releases that end's moment connection, e.g. for truss bars.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Supports     -- node_id, type (Fixed / Pinned / Roller X / Roller Y)</t>
+          <t xml:space="preserve">  Sections     -- name, E, A, I: the catalog behind the Members dropdown. Ships with common UK UB/UC steel sections (SI units, indicative values -- verify for design use). Add rows for your own.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NodalLoads   -- node_id, fx, fy, m (force/moment applied directly at a node)</t>
+          <t xml:space="preserve">  Supports     -- node_id, type (Fixed / Pinned / Roller X / Roller Y)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PointLoads   -- member_id, position (distance from node_i), fx, fy, m, frame (local: along the member axis: global: along the X/Y axes)</t>
+          <t xml:space="preserve">  NodalLoads   -- node_id, fx, fy, m (force/moment applied directly at a node)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  PointLoads   -- member_id, position (distance from node_i), fx, fy, m, frame (local: along the member axis: global: along the X/Y axes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  UDLs         -- member_id, wx, wy (force per length), frame, start/end (distance from node_i; leave blank for the full member)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Output sheets (filled in automatically when you run the analysis)</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Reactions, Displacements -- numeric results per node</t>
+          <t>Output sheets (filled in automatically when you run the analysis)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Diagrams                 -- geometry/load diagram, deformed shape, and per-member N/V/M diagrams</t>
+          <t xml:space="preserve">  Reactions, Displacements -- numeric results per node</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Summary                  -- per-member max |N|, |V|, |M|, |deflection|</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Diagrams                 -- geometry/load diagram, deformed shape, and per-member N/V/M diagrams</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Running the analysis</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  This workbook is paired with frame.py via xlwings. With the xlwings Excel add-in installed, click the xlwings ribbon tab's 'Run main' button (or run `python frame.py` after editing it to call main() against this workbook) to solve the model and refresh the output sheets in place.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  This workbook is paired with frame.py via xlwings. With the xlwings Excel add-in installed, click the xlwings ribbon tab's 'Run main' button (or run `python frame.py` after editing it to call main() against this workbook) to solve the model and refresh the output sheets in place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>The sample data already in the input sheets is a simply supported beam with a midspan point load -- replace it with your own model.</t>
         </is>
@@ -572,6 +590,96 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Ux</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Uy</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Rz</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>member_id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>max_abs_N</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>max_abs_V</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>max_abs_M</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>max_abs_deflection</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -652,17 +760,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,25 +792,30 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>hinge_i</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>hinge_j</t>
         </is>
@@ -723,32 +837,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>200000000000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.01</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>8.000000000000001e-05</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="G2:G201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="D2:D201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=SectionNames</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -757,6 +874,422 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="110" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>UK UB/UC sections, major-axis I, steel E=210e9 (SI units: Pa, m2, m4). Indicative values -- verify against current section tables for design use. Add your own rows; the Members dropdown picks them up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>127x76x13 UB</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.00165</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.73e-06</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>152x89x16 UB</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.00203</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8.34e-06</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>178x102x19 UB</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.356e-05</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>203x102x23 UB</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.105e-05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>203x133x25 UB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.34e-05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>254x102x28 UB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.00361</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.005e-05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>254x146x37 UB</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.00472</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.537e-05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>305x165x40 UB</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.00513</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.503e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>356x171x51 UB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.00649</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0001414</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>406x178x60 UB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.000216</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>457x191x82 UB</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0003705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>533x210x92 UB</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0005523</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>610x229x113 UB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0008732</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>686x254x140 UB</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.001363</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>762x267x173 UB</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.002053</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>152x152x23 UC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.00292</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.25e-05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>152x152x37 UC</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.00471</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.21e-05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>203x203x46 UC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.00587</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.57e-05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>203x203x60 UC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.125e-05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>254x254x73 UC</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.009310000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0001141</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>254x254x89 UC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0001427</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>305x305x97 UC</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0002225</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>305x305x118 UC</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>210000000000</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0002767</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -815,7 +1348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -857,7 +1390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -940,7 +1473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -995,48 +1528,6 @@
       <formula1>"local,global"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>node_id</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Ry</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Rm</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1064,17 +1555,17 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Ux</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Uy</t>
+          <t>Ry</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Rz</t>
+          <t>Rm</t>
         </is>
       </c>
     </row>
